--- a/UITests/Fixtures/plan.xlsx
+++ b/UITests/Fixtures/plan.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,6 +481,11 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Effort</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Avg Pace/Pwr</t>
         </is>
       </c>
     </row>

--- a/UITests/Fixtures/plan.xlsx
+++ b/UITests/Fixtures/plan.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Weekly Schedules" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Test Results &amp; Zones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Extras" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1293,4 +1294,120 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>What it was</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Duration (min)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Distance (km)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Avg HR</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Counts as training</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Walk</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dog walk</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>92</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>xtest001</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>